--- a/data/cbas/cba_metadata.xlsx
+++ b/data/cbas/cba_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/data/cbas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F420670F-4F8A-4443-A32A-7213F15BF01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951CEC8B-07A4-2941-A52A-7E551DF252FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3400" yWindow="720" windowWidth="35840" windowHeight="21900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="238">
   <si>
     <t>project_name</t>
   </si>
@@ -733,6 +733,9 @@
   </si>
   <si>
     <t>https://nantucketcurrent.com/news/community-foundation-announces-first-offshore-wind-fund-grants</t>
+  </si>
+  <si>
+    <t>New Shoreham</t>
   </si>
 </sst>
 </file>
@@ -784,18 +787,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Karla"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -810,6 +801,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -820,13 +828,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -843,22 +851,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1095,7 +1110,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>235</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1149,473 +1164,473 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:29" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="14">
         <v>34.611944000000001</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="14">
         <v>-120.08833300000001</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="14">
         <v>4</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="14">
         <v>60</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="17">
         <v>41.355556</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="17">
         <v>-72.099444000000005</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="17">
         <v>2023</v>
       </c>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-    </row>
-    <row r="4" spans="1:29" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10" t="s">
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+      <c r="Z3" s="19"/>
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+    </row>
+    <row r="4" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="17">
         <v>43.762222000000001</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="17">
         <v>-69.320278000000002</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="17">
         <v>1</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="17">
         <v>11</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-    </row>
-    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="19"/>
+      <c r="AA4" s="19"/>
+      <c r="AB4" s="19"/>
+      <c r="AC4" s="19"/>
+    </row>
+    <row r="5" spans="1:29" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="9">
         <v>41.7</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="9">
         <v>-70.3</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-    </row>
-    <row r="6" spans="1:29" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10" t="s">
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12"/>
+      <c r="AC5" s="12"/>
+    </row>
+    <row r="6" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="17">
         <v>42.519444</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="17">
         <v>-70.897221999999999</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="14"/>
-    </row>
-    <row r="7" spans="1:29" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10" t="s">
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+    </row>
+    <row r="7" spans="1:29" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <v>41.7</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="9">
         <v>-70.3</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="9">
         <v>2023</v>
       </c>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="14"/>
-    </row>
-    <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="8" t="s">
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="12"/>
+      <c r="AB7" s="12"/>
+      <c r="AC7" s="12"/>
+    </row>
+    <row r="8" spans="1:29" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>41.595191999999997</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>-70.475926999999999</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>62</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <v>800</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
-    </row>
-    <row r="9" spans="1:29" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10" t="s">
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="21"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="21"/>
+      <c r="AA8" s="21"/>
+      <c r="AB8" s="21"/>
+      <c r="AC8" s="21"/>
+    </row>
+    <row r="9" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="17">
         <v>41.4</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="17">
         <v>-70.616667000000007</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="17">
         <v>62</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="17">
         <v>800</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
-    </row>
-    <row r="10" spans="1:29" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="10" t="s">
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="19"/>
+      <c r="AB9" s="19"/>
+      <c r="AC9" s="19"/>
+    </row>
+    <row r="10" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="17">
         <v>41.282778</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="17">
         <v>-70.099444000000005</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="17">
         <v>62</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="17">
         <v>800</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="14"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="19"/>
+      <c r="AB10" s="19"/>
+      <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>230</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1669,115 +1684,115 @@
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
     </row>
-    <row r="12" spans="1:29" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="17">
         <v>40.956944</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="17">
         <v>-72.198888999999994</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="17">
         <v>2023</v>
       </c>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="14"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="14"/>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
-      <c r="AB12" s="14"/>
-      <c r="AC12" s="14"/>
-    </row>
-    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="8" t="s">
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
+      <c r="AC12" s="19"/>
+    </row>
+    <row r="13" spans="1:29" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>40.816667000000002</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>-72.933333000000005</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="L13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
+      <c r="AA13" s="21"/>
+      <c r="AB13" s="21"/>
+      <c r="AC13" s="21"/>
     </row>
     <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>233</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1787,7 +1802,7 @@
         <v>48</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>237</v>
       </c>
       <c r="E14" s="2">
         <v>41.169722</v>
@@ -1831,63 +1846,62 @@
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
     </row>
-    <row r="15" spans="1:29" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="10" t="s">
+    <row r="15" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="17">
         <v>41.6</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="17">
         <v>-71.25</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="L15" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
-    </row>
-    <row r="16" spans="1:29" ht="15" x14ac:dyDescent="0.2">
-      <c r="B16" s="6"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="19"/>
+      <c r="AA15" s="19"/>
+      <c r="AB15" s="19"/>
+      <c r="AC15" s="19"/>
+    </row>
+    <row r="16" spans="1:29" ht="13" x14ac:dyDescent="0.15">
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
@@ -1922,7 +1936,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>50</v>
       </c>
     </row>

--- a/data/cbas/cba_metadata.xlsx
+++ b/data/cbas/cba_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/data/cbas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951CEC8B-07A4-2941-A52A-7E551DF252FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E28B972-32E2-6F4D-8C0B-740470C18F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17100" yWindow="4800" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="241">
   <si>
     <t>project_name</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Not yet built</t>
   </si>
   <si>
-    <t>State Pier</t>
-  </si>
-  <si>
     <t>Connecticut</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>New England Aqua Ventus</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
@@ -114,9 +108,6 @@
     <t>Offshore wind energy cable landing</t>
   </si>
   <si>
-    <t>Salem Offshore Wind Terminal</t>
-  </si>
-  <si>
     <t>Salem</t>
   </si>
   <si>
@@ -126,9 +117,6 @@
     <t>2024-</t>
   </si>
   <si>
-    <t>Vineyard Wind 1</t>
-  </si>
-  <si>
     <t>Mashpee Wampanoag Tribe</t>
   </si>
   <si>
@@ -141,33 +129,21 @@
     <t>Nantucket</t>
   </si>
   <si>
-    <t>South Brooklyn Marine Terminal</t>
-  </si>
-  <si>
     <t>New York</t>
   </si>
   <si>
     <t>Brooklyn</t>
   </si>
   <si>
-    <t>South Fork</t>
-  </si>
-  <si>
     <t>East Hampton</t>
   </si>
   <si>
-    <t>Sunrise</t>
-  </si>
-  <si>
     <t>Brookhaven</t>
   </si>
   <si>
     <t>Under construction in 2024</t>
   </si>
   <si>
-    <t>Block Island</t>
-  </si>
-  <si>
     <t>Rhode Island</t>
   </si>
   <si>
@@ -684,9 +660,6 @@
     <t>Mineral County</t>
   </si>
   <si>
-    <t>South Coast</t>
-  </si>
-  <si>
     <t>CA-CADEMO</t>
   </si>
   <si>
@@ -736,13 +709,49 @@
   </si>
   <si>
     <t>New Shoreham</t>
+  </si>
+  <si>
+    <t>Sunrise Wind</t>
+  </si>
+  <si>
+    <t>Equinor/BP</t>
+  </si>
+  <si>
+    <t>South Fork Wind</t>
+  </si>
+  <si>
+    <t>Vineyard Offshore</t>
+  </si>
+  <si>
+    <t>Vineyard Wind</t>
+  </si>
+  <si>
+    <t>company</t>
+  </si>
+  <si>
+    <t>community</t>
+  </si>
+  <si>
+    <t>Maine Aqua Ventus</t>
+  </si>
+  <si>
+    <t>North East Offshore</t>
+  </si>
+  <si>
+    <t>Deepwater Wind</t>
+  </si>
+  <si>
+    <t>SouthCoast Wind Energy</t>
+  </si>
+  <si>
+    <t>Salem Wind Terminal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -802,24 +811,27 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <i/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -829,12 +841,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -851,29 +857,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1095,229 +1096,230 @@
   <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="12.6640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:29" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+    </row>
+    <row r="2" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5">
+        <v>34.611944000000001</v>
+      </c>
+      <c r="F2" s="5">
+        <v>-120.08833300000001</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="5">
+        <v>4</v>
+      </c>
+      <c r="K2" s="5">
+        <v>60</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5">
+        <v>41.355556</v>
+      </c>
+      <c r="F3" s="5">
+        <v>-72.099444000000005</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2023</v>
+      </c>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+    </row>
+    <row r="4" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="5">
+        <v>43.762222000000001</v>
+      </c>
+      <c r="F4" s="5">
+        <v>-69.320278000000002</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="K4" s="5">
         <v>11</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="14">
-        <v>34.611944000000001</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-120.08833300000001</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="14">
-        <v>4</v>
-      </c>
-      <c r="K2" s="14">
-        <v>60</v>
-      </c>
-      <c r="L2" s="14" t="s">
+      <c r="L4" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="17">
-        <v>41.355556</v>
-      </c>
-      <c r="F3" s="17">
-        <v>-72.099444000000005</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="17">
-        <v>2023</v>
-      </c>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19"/>
-      <c r="T3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="19"/>
-      <c r="W3" s="19"/>
-      <c r="X3" s="19"/>
-      <c r="Y3" s="19"/>
-      <c r="Z3" s="19"/>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="19"/>
-      <c r="AC3" s="19"/>
-    </row>
-    <row r="4" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="17" t="s">
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="7"/>
+      <c r="AC4" s="7"/>
+    </row>
+    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="17">
-        <v>43.762222000000001</v>
-      </c>
-      <c r="F4" s="17">
-        <v>-69.320278000000002</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="17" t="s">
+      <c r="C5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="17">
-        <v>1</v>
-      </c>
-      <c r="K4" s="17">
-        <v>11</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="19"/>
-      <c r="AC4" s="19"/>
-    </row>
-    <row r="5" spans="1:29" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="E5" s="9">
         <v>41.7</v>
@@ -1329,581 +1331,581 @@
         <v>14</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
-    </row>
-    <row r="6" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16" t="s">
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="11"/>
+      <c r="Z5" s="11"/>
+      <c r="AA5" s="11"/>
+      <c r="AB5" s="11"/>
+      <c r="AC5" s="11"/>
+    </row>
+    <row r="6" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="5">
+        <v>42.519444</v>
+      </c>
+      <c r="F6" s="5">
+        <v>-70.897221999999999</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
+      <c r="AC6" s="7"/>
+    </row>
+    <row r="7" spans="1:29" s="4" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="5">
+        <v>41.7</v>
+      </c>
+      <c r="F7" s="5">
+        <v>-70.3</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2023</v>
+      </c>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7"/>
+    </row>
+    <row r="8" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="5">
+        <v>41.595191999999997</v>
+      </c>
+      <c r="F8" s="5">
+        <v>-70.475926999999999</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="5">
+        <v>62</v>
+      </c>
+      <c r="K8" s="5">
+        <v>800</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+    </row>
+    <row r="9" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="5">
+        <v>41.4</v>
+      </c>
+      <c r="F9" s="5">
+        <v>-70.616667000000007</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="5">
+        <v>62</v>
+      </c>
+      <c r="K9" s="5">
+        <v>800</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="7"/>
+      <c r="AC9" s="7"/>
+    </row>
+    <row r="10" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="5">
+        <v>41.282778</v>
+      </c>
+      <c r="F10" s="5">
+        <v>-70.099444000000005</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="5">
+        <v>62</v>
+      </c>
+      <c r="K10" s="5">
+        <v>800</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="7"/>
+      <c r="AB10" s="7"/>
+      <c r="AC10" s="7"/>
+    </row>
+    <row r="11" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="5">
+        <v>40.65</v>
+      </c>
+      <c r="F11" s="5">
+        <v>-73.95</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+    </row>
+    <row r="12" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="5">
+        <v>40.956944</v>
+      </c>
+      <c r="F12" s="5">
+        <v>-72.198888999999994</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12" s="5">
+        <v>2023</v>
+      </c>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7"/>
+    </row>
+    <row r="13" spans="1:29" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="14">
+        <v>40.816667000000002</v>
+      </c>
+      <c r="F13" s="14">
+        <v>-72.933333000000005</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="16"/>
+      <c r="AB13" s="16"/>
+      <c r="AC13" s="16"/>
+    </row>
+    <row r="14" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14" s="5">
+        <v>41.169722</v>
+      </c>
+      <c r="F14" s="5">
+        <v>-71.58</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="5">
+        <v>5</v>
+      </c>
+      <c r="K14" s="5">
+        <v>30</v>
+      </c>
+      <c r="L14" s="5">
+        <v>2016</v>
+      </c>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7"/>
+    </row>
+    <row r="15" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="17" t="s">
+      <c r="B15" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="5">
+        <v>41.6</v>
+      </c>
+      <c r="F15" s="5">
+        <v>-71.25</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="17">
-        <v>42.519444</v>
-      </c>
-      <c r="F6" s="17">
-        <v>-70.897221999999999</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="17" t="s">
+      <c r="J15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="19"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="19"/>
-      <c r="AC6" s="19"/>
-    </row>
-    <row r="7" spans="1:29" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="9">
-        <v>41.7</v>
-      </c>
-      <c r="F7" s="9">
-        <v>-70.3</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="9">
-        <v>2023</v>
-      </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="12"/>
-      <c r="AB7" s="12"/>
-      <c r="AC7" s="12"/>
-    </row>
-    <row r="8" spans="1:29" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="1">
-        <v>41.595191999999997</v>
-      </c>
-      <c r="F8" s="1">
-        <v>-70.475926999999999</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="1">
-        <v>62</v>
-      </c>
-      <c r="K8" s="1">
-        <v>800</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="21"/>
-      <c r="V8" s="21"/>
-      <c r="W8" s="21"/>
-      <c r="X8" s="21"/>
-      <c r="Y8" s="21"/>
-      <c r="Z8" s="21"/>
-      <c r="AA8" s="21"/>
-      <c r="AB8" s="21"/>
-      <c r="AC8" s="21"/>
-    </row>
-    <row r="9" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="17">
-        <v>41.4</v>
-      </c>
-      <c r="F9" s="17">
-        <v>-70.616667000000007</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="17">
-        <v>62</v>
-      </c>
-      <c r="K9" s="17">
-        <v>800</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="19"/>
-    </row>
-    <row r="10" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="17">
-        <v>41.282778</v>
-      </c>
-      <c r="F10" s="17">
-        <v>-70.099444000000005</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="17">
-        <v>62</v>
-      </c>
-      <c r="K10" s="17">
-        <v>800</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M10" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="19"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
-      <c r="AC10" s="19"/>
-    </row>
-    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="2">
-        <v>40.65</v>
-      </c>
-      <c r="F11" s="2">
-        <v>-73.95</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="2" t="s">
+      <c r="K15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="4"/>
-    </row>
-    <row r="12" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="17">
-        <v>40.956944</v>
-      </c>
-      <c r="F12" s="17">
-        <v>-72.198888999999994</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="17">
-        <v>2023</v>
-      </c>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="19"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
-      <c r="AC12" s="19"/>
-    </row>
-    <row r="13" spans="1:29" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="1">
-        <v>40.816667000000002</v>
-      </c>
-      <c r="F13" s="1">
-        <v>-72.933333000000005</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-    </row>
-    <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E14" s="2">
-        <v>41.169722</v>
-      </c>
-      <c r="F14" s="2">
-        <v>-71.58</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="2">
-        <v>5</v>
-      </c>
-      <c r="K14" s="2">
-        <v>30</v>
-      </c>
-      <c r="L14" s="2">
-        <v>2016</v>
-      </c>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
-      <c r="AB14" s="4"/>
-      <c r="AC14" s="4"/>
-    </row>
-    <row r="15" spans="1:29" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="17">
-        <v>41.6</v>
-      </c>
-      <c r="F15" s="17">
-        <v>-71.25</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="17" t="s">
+      <c r="L15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="19"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="19"/>
-      <c r="AB15" s="19"/>
-      <c r="AC15" s="19"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
     </row>
     <row r="16" spans="1:29" ht="13" x14ac:dyDescent="0.15">
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1936,8 +1938,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
-        <v>50</v>
+      <c r="A1" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2007,19 +2009,19 @@
     </row>
     <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F2" s="2">
         <v>44</v>
@@ -2033,19 +2035,19 @@
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F3" s="2">
         <v>112</v>
@@ -2059,19 +2061,19 @@
     </row>
     <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2">
         <v>20</v>
@@ -2085,19 +2087,19 @@
     </row>
     <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2">
         <v>30</v>
@@ -2111,19 +2113,19 @@
     </row>
     <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2">
         <v>100</v>
@@ -2137,19 +2139,19 @@
     </row>
     <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2">
         <v>67</v>
@@ -2163,19 +2165,19 @@
     </row>
     <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2">
         <v>74</v>
@@ -2189,19 +2191,19 @@
     </row>
     <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F9" s="2">
         <v>74</v>
@@ -2215,19 +2217,19 @@
     </row>
     <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F10" s="2">
         <v>24</v>
@@ -2241,19 +2243,19 @@
     </row>
     <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F11" s="2">
         <v>87</v>
@@ -2267,19 +2269,19 @@
     </row>
     <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F12" s="2">
         <v>100</v>
@@ -2293,19 +2295,19 @@
     </row>
     <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F13" s="2">
         <v>65</v>
@@ -2319,19 +2321,19 @@
     </row>
     <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F14" s="2">
         <v>95</v>
@@ -2345,19 +2347,19 @@
     </row>
     <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F15" s="2">
         <v>72</v>
@@ -2371,19 +2373,19 @@
     </row>
     <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F16" s="2">
         <v>67</v>
@@ -2397,19 +2399,19 @@
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F17" s="2">
         <v>105</v>
@@ -2423,19 +2425,19 @@
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F18" s="2">
         <v>56</v>
@@ -2449,19 +2451,19 @@
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F19" s="2">
         <v>19</v>
@@ -2475,19 +2477,19 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F20" s="2">
         <v>17</v>
@@ -2501,19 +2503,19 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F21" s="2">
         <v>44</v>
@@ -2527,19 +2529,19 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F22" s="2">
         <v>48</v>
@@ -2553,19 +2555,19 @@
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F23" s="2">
         <v>13</v>
@@ -2579,19 +2581,19 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F24" s="2">
         <v>10</v>
@@ -2605,19 +2607,19 @@
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F25" s="2">
         <v>38</v>
@@ -2631,19 +2633,19 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F26" s="2">
         <v>29</v>
@@ -2657,19 +2659,19 @@
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F27" s="2">
         <v>12</v>
@@ -2683,19 +2685,19 @@
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F28" s="2">
         <v>39</v>
@@ -2709,19 +2711,19 @@
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F29" s="2">
         <v>12</v>
@@ -2735,19 +2737,19 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F30" s="2">
         <v>74</v>
@@ -2761,19 +2763,19 @@
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F31" s="2">
         <v>100</v>
@@ -2787,19 +2789,19 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F32" s="2">
         <v>119</v>
@@ -2813,19 +2815,19 @@
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F33" s="2">
         <v>99</v>
@@ -2839,19 +2841,19 @@
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F34" s="2">
         <v>111</v>
@@ -2865,19 +2867,19 @@
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F35" s="2">
         <v>31</v>
@@ -2891,19 +2893,19 @@
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F36" s="2">
         <v>200</v>
@@ -2917,19 +2919,19 @@
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F37" s="2">
         <v>36</v>
@@ -2943,19 +2945,19 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F38" s="2">
         <v>32</v>
@@ -2969,19 +2971,19 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F39" s="2">
         <v>37</v>
@@ -2995,19 +2997,19 @@
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F40" s="2">
         <v>50</v>
@@ -3021,19 +3023,19 @@
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F41" s="2">
         <v>40</v>
@@ -3047,19 +3049,19 @@
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F42" s="2">
         <v>25</v>
@@ -3073,19 +3075,19 @@
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F43" s="2">
         <v>20</v>
@@ -3099,19 +3101,19 @@
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F44" s="2">
         <v>75</v>
@@ -3125,19 +3127,19 @@
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F45" s="2">
         <v>37</v>
@@ -3151,19 +3153,19 @@
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F46" s="2">
         <v>70</v>
@@ -3177,19 +3179,19 @@
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F47" s="2">
         <v>65</v>
@@ -3203,19 +3205,19 @@
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F48" s="2">
         <v>67</v>
@@ -3229,19 +3231,19 @@
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F49" s="2">
         <v>71</v>
@@ -3255,19 +3257,19 @@
     </row>
     <row r="50" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F50" s="2">
         <v>67</v>
@@ -3281,19 +3283,19 @@
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F51" s="2">
         <v>54</v>
@@ -3307,19 +3309,19 @@
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F52" s="2">
         <v>27</v>
@@ -3333,19 +3335,19 @@
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F53" s="2">
         <v>58</v>
@@ -3359,19 +3361,19 @@
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F54" s="2">
         <v>71</v>
@@ -3385,19 +3387,19 @@
     </row>
     <row r="55" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F55" s="2">
         <v>100</v>
@@ -3411,19 +3413,19 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F56" s="2">
         <v>75</v>
@@ -3437,19 +3439,19 @@
     </row>
     <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F57" s="2">
         <v>120</v>
@@ -3463,19 +3465,19 @@
     </row>
     <row r="58" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F58" s="2">
         <v>152</v>
@@ -3489,19 +3491,19 @@
     </row>
     <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F59" s="2">
         <v>66</v>
@@ -3515,19 +3517,19 @@
     </row>
     <row r="60" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F60" s="2">
         <v>43</v>
@@ -3541,19 +3543,19 @@
     </row>
     <row r="61" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F61" s="2">
         <v>100</v>
@@ -3567,19 +3569,19 @@
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F62" s="2">
         <v>84</v>
@@ -3593,19 +3595,19 @@
     </row>
     <row r="63" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="D63" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F63" s="2">
         <v>82</v>
@@ -3619,19 +3621,19 @@
     </row>
     <row r="64" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F64" s="2">
         <v>20</v>
@@ -3645,19 +3647,19 @@
     </row>
     <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F65" s="2">
         <v>77</v>
@@ -3671,19 +3673,19 @@
     </row>
     <row r="66" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F66" s="2">
         <v>109</v>
@@ -3697,19 +3699,19 @@
     </row>
     <row r="67" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F67" s="2">
         <v>120</v>
@@ -3723,19 +3725,19 @@
     </row>
     <row r="68" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F68" s="2">
         <v>96</v>
@@ -3749,19 +3751,19 @@
     </row>
     <row r="69" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F69" s="2">
         <v>100</v>
@@ -3775,19 +3777,19 @@
     </row>
     <row r="70" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F70" s="2">
         <v>62</v>
@@ -3801,19 +3803,19 @@
     </row>
     <row r="71" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F71" s="2">
         <v>87</v>
@@ -3827,19 +3829,19 @@
     </row>
     <row r="72" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F72" s="2">
         <v>112</v>
@@ -3853,19 +3855,19 @@
     </row>
     <row r="73" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F73" s="2">
         <v>197</v>
@@ -3879,19 +3881,19 @@
     </row>
     <row r="74" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F74" s="2">
         <v>31</v>
@@ -3905,19 +3907,19 @@
     </row>
     <row r="75" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F75" s="2">
         <v>39</v>
@@ -3931,19 +3933,19 @@
     </row>
     <row r="76" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F76" s="2">
         <v>120</v>
@@ -3957,19 +3959,19 @@
     </row>
     <row r="77" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F77" s="2">
         <v>165</v>
@@ -3983,19 +3985,19 @@
     </row>
     <row r="78" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F78" s="2">
         <v>116</v>
@@ -4009,19 +4011,19 @@
     </row>
     <row r="79" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F79" s="2">
         <v>23</v>
@@ -4035,19 +4037,19 @@
     </row>
     <row r="80" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F80" s="2">
         <v>61</v>
@@ -4061,19 +4063,19 @@
     </row>
     <row r="81" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F81" s="2">
         <v>23</v>

--- a/data/cbas/cba_metadata.xlsx
+++ b/data/cbas/cba_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/data/cbas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Library/CloudStorage/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/data/cbas/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E28B972-32E2-6F4D-8C0B-740470C18F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17100" yWindow="4800" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -857,7 +857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -866,12 +866,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1111,60 +1109,60 @@
     <col min="13" max="16384" width="12.6640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:29" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
     </row>
     <row r="2" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
@@ -1312,53 +1310,53 @@
       <c r="A5" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="2">
         <v>41.7</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="2">
         <v>-70.3</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="11"/>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="11"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="11"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
     </row>
     <row r="6" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
@@ -1741,57 +1739,57 @@
       <c r="AB12" s="7"/>
       <c r="AC12" s="7"/>
     </row>
-    <row r="13" spans="1:29" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:29" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <v>40.816667000000002</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <v>-72.933333000000005</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="16"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
     </row>
     <row r="14" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
@@ -1904,8 +1902,8 @@
       <c r="AC15" s="7"/>
     </row>
     <row r="16" spans="1:29" ht="13" x14ac:dyDescent="0.15">
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/cbas/cba_metadata.xlsx
+++ b/data/cbas/cba_metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Library/CloudStorage/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/data/cbas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E28B972-32E2-6F4D-8C0B-740470C18F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B33D0E-4C5A-674A-AE1F-3D49C8066545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,9 +96,6 @@
     <t>Non-financial</t>
   </si>
   <si>
-    <t>New England Wind 1</t>
-  </si>
-  <si>
     <t>Massachusetts</t>
   </si>
   <si>
@@ -745,6 +742,9 @@
   </si>
   <si>
     <t>Salem Wind Terminal</t>
+  </si>
+  <si>
+    <t>Avangrid</t>
   </si>
 </sst>
 </file>
@@ -1111,16 +1111,16 @@
   <sheetData>
     <row r="1" spans="1:29" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1166,7 +1166,7 @@
     </row>
     <row r="2" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>11</v>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="3" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>17</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="4" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>21</v>
@@ -1308,16 +1308,16 @@
     </row>
     <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="E5" s="2">
         <v>41.7</v>
@@ -1329,7 +1329,7 @@
         <v>14</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>20</v>
@@ -1360,16 +1360,16 @@
     </row>
     <row r="6" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" s="5">
         <v>42.519444</v>
@@ -1381,7 +1381,7 @@
         <v>14</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>19</v>
@@ -1393,7 +1393,7 @@
         <v>20</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -1415,16 +1415,16 @@
     </row>
     <row r="7" spans="1:29" s="4" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="E7" s="5">
         <v>41.7</v>
@@ -1436,7 +1436,7 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>20</v>
@@ -1467,16 +1467,16 @@
     </row>
     <row r="8" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" s="5">
         <v>41.595191999999997</v>
@@ -1497,7 +1497,7 @@
         <v>800</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
@@ -1519,16 +1519,16 @@
     </row>
     <row r="9" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" s="5">
         <v>41.4</v>
@@ -1540,7 +1540,7 @@
         <v>14</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>15</v>
@@ -1552,7 +1552,7 @@
         <v>800</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="10" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="5">
         <v>41.282778</v>
@@ -1595,7 +1595,7 @@
         <v>14</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>15</v>
@@ -1607,10 +1607,10 @@
         <v>800</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
@@ -1631,16 +1631,16 @@
     </row>
     <row r="11" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="E11" s="5">
         <v>40.65</v>
@@ -1649,7 +1649,7 @@
         <v>-73.95</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>23</v>
@@ -1664,7 +1664,7 @@
         <v>20</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -1686,16 +1686,16 @@
     </row>
     <row r="12" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E12" s="5">
         <v>40.956944</v>
@@ -1707,10 +1707,10 @@
         <v>14</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>20</v>
@@ -1741,16 +1741,16 @@
     </row>
     <row r="13" spans="1:29" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" s="12">
         <v>40.816667000000002</v>
@@ -1762,7 +1762,7 @@
         <v>14</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>20</v>
@@ -1771,7 +1771,7 @@
         <v>20</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M13" s="14"/>
       <c r="N13" s="14"/>
@@ -1793,16 +1793,16 @@
     </row>
     <row r="14" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E14" s="5">
         <v>41.169722</v>
@@ -1848,16 +1848,16 @@
     </row>
     <row r="15" spans="1:29" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="E15" s="5">
         <v>41.6</v>
@@ -1869,10 +1869,10 @@
         <v>14</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>20</v>
@@ -1937,7 +1937,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2007,19 +2007,19 @@
     </row>
     <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F2" s="2">
         <v>44</v>
@@ -2033,19 +2033,19 @@
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F3" s="2">
         <v>112</v>
@@ -2059,19 +2059,19 @@
     </row>
     <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F4" s="2">
         <v>20</v>
@@ -2085,19 +2085,19 @@
     </row>
     <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2">
         <v>30</v>
@@ -2111,19 +2111,19 @@
     </row>
     <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2">
         <v>100</v>
@@ -2137,19 +2137,19 @@
     </row>
     <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2">
         <v>67</v>
@@ -2163,19 +2163,19 @@
     </row>
     <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" s="2">
         <v>74</v>
@@ -2189,19 +2189,19 @@
     </row>
     <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" s="2">
         <v>74</v>
@@ -2215,19 +2215,19 @@
     </row>
     <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10" s="2">
         <v>24</v>
@@ -2241,19 +2241,19 @@
     </row>
     <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" s="2">
         <v>87</v>
@@ -2267,19 +2267,19 @@
     </row>
     <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F12" s="2">
         <v>100</v>
@@ -2293,19 +2293,19 @@
     </row>
     <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="2">
         <v>65</v>
@@ -2319,19 +2319,19 @@
     </row>
     <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" s="2">
         <v>95</v>
@@ -2345,19 +2345,19 @@
     </row>
     <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F15" s="2">
         <v>72</v>
@@ -2371,19 +2371,19 @@
     </row>
     <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F16" s="2">
         <v>67</v>
@@ -2397,19 +2397,19 @@
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" s="2">
         <v>105</v>
@@ -2423,19 +2423,19 @@
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F18" s="2">
         <v>56</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F19" s="2">
         <v>19</v>
@@ -2475,19 +2475,19 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F20" s="2">
         <v>17</v>
@@ -2501,19 +2501,19 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F21" s="2">
         <v>44</v>
@@ -2527,19 +2527,19 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F22" s="2">
         <v>48</v>
@@ -2553,19 +2553,19 @@
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F23" s="2">
         <v>13</v>
@@ -2579,19 +2579,19 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F24" s="2">
         <v>10</v>
@@ -2605,19 +2605,19 @@
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F25" s="2">
         <v>38</v>
@@ -2631,19 +2631,19 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F26" s="2">
         <v>29</v>
@@ -2657,19 +2657,19 @@
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F27" s="2">
         <v>12</v>
@@ -2683,19 +2683,19 @@
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F28" s="2">
         <v>39</v>
@@ -2709,19 +2709,19 @@
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F29" s="2">
         <v>12</v>
@@ -2735,19 +2735,19 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F30" s="2">
         <v>74</v>
@@ -2761,19 +2761,19 @@
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F31" s="2">
         <v>100</v>
@@ -2787,19 +2787,19 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F32" s="2">
         <v>119</v>
@@ -2813,19 +2813,19 @@
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F33" s="2">
         <v>99</v>
@@ -2839,19 +2839,19 @@
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F34" s="2">
         <v>111</v>
@@ -2865,19 +2865,19 @@
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F35" s="2">
         <v>31</v>
@@ -2891,19 +2891,19 @@
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F36" s="2">
         <v>200</v>
@@ -2917,19 +2917,19 @@
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F37" s="2">
         <v>36</v>
@@ -2943,19 +2943,19 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F38" s="2">
         <v>32</v>
@@ -2969,19 +2969,19 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F39" s="2">
         <v>37</v>
@@ -2995,19 +2995,19 @@
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F40" s="2">
         <v>50</v>
@@ -3021,19 +3021,19 @@
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F41" s="2">
         <v>40</v>
@@ -3047,19 +3047,19 @@
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F42" s="2">
         <v>25</v>
@@ -3073,19 +3073,19 @@
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F43" s="2">
         <v>20</v>
@@ -3099,19 +3099,19 @@
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F44" s="2">
         <v>75</v>
@@ -3125,19 +3125,19 @@
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F45" s="2">
         <v>37</v>
@@ -3151,19 +3151,19 @@
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F46" s="2">
         <v>70</v>
@@ -3177,19 +3177,19 @@
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F47" s="2">
         <v>65</v>
@@ -3203,19 +3203,19 @@
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F48" s="2">
         <v>67</v>
@@ -3229,19 +3229,19 @@
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F49" s="2">
         <v>71</v>
@@ -3255,19 +3255,19 @@
     </row>
     <row r="50" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F50" s="2">
         <v>67</v>
@@ -3281,19 +3281,19 @@
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F51" s="2">
         <v>54</v>
@@ -3307,19 +3307,19 @@
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F52" s="2">
         <v>27</v>
@@ -3333,19 +3333,19 @@
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F53" s="2">
         <v>58</v>
@@ -3359,19 +3359,19 @@
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="D54" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F54" s="2">
         <v>71</v>
@@ -3385,19 +3385,19 @@
     </row>
     <row r="55" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="D55" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F55" s="2">
         <v>100</v>
@@ -3411,19 +3411,19 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="D56" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F56" s="2">
         <v>75</v>
@@ -3437,19 +3437,19 @@
     </row>
     <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="D57" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F57" s="2">
         <v>120</v>
@@ -3463,19 +3463,19 @@
     </row>
     <row r="58" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="D58" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F58" s="2">
         <v>152</v>
@@ -3489,19 +3489,19 @@
     </row>
     <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="D59" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F59" s="2">
         <v>66</v>
@@ -3515,19 +3515,19 @@
     </row>
     <row r="60" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="D60" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F60" s="2">
         <v>43</v>
@@ -3541,19 +3541,19 @@
     </row>
     <row r="61" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="D61" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F61" s="2">
         <v>100</v>
@@ -3567,19 +3567,19 @@
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="D62" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F62" s="2">
         <v>84</v>
@@ -3593,19 +3593,19 @@
     </row>
     <row r="63" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>172</v>
-      </c>
       <c r="D63" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F63" s="2">
         <v>82</v>
@@ -3619,19 +3619,19 @@
     </row>
     <row r="64" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="D64" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F64" s="2">
         <v>20</v>
@@ -3645,19 +3645,19 @@
     </row>
     <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="D65" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F65" s="2">
         <v>77</v>
@@ -3671,19 +3671,19 @@
     </row>
     <row r="66" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="D66" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F66" s="2">
         <v>109</v>
@@ -3697,19 +3697,19 @@
     </row>
     <row r="67" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="D67" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F67" s="2">
         <v>120</v>
@@ -3723,19 +3723,19 @@
     </row>
     <row r="68" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="D68" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F68" s="2">
         <v>96</v>
@@ -3749,19 +3749,19 @@
     </row>
     <row r="69" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="D69" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F69" s="2">
         <v>100</v>
@@ -3775,19 +3775,19 @@
     </row>
     <row r="70" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="D70" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F70" s="2">
         <v>62</v>
@@ -3801,19 +3801,19 @@
     </row>
     <row r="71" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="D71" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F71" s="2">
         <v>87</v>
@@ -3827,19 +3827,19 @@
     </row>
     <row r="72" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="D72" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F72" s="2">
         <v>112</v>
@@ -3853,19 +3853,19 @@
     </row>
     <row r="73" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="D73" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F73" s="2">
         <v>197</v>
@@ -3879,19 +3879,19 @@
     </row>
     <row r="74" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F74" s="2">
         <v>31</v>
@@ -3905,19 +3905,19 @@
     </row>
     <row r="75" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>196</v>
-      </c>
       <c r="D75" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F75" s="2">
         <v>39</v>
@@ -3931,19 +3931,19 @@
     </row>
     <row r="76" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="D76" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F76" s="2">
         <v>120</v>
@@ -3957,19 +3957,19 @@
     </row>
     <row r="77" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F77" s="2">
         <v>165</v>
@@ -3983,19 +3983,19 @@
     </row>
     <row r="78" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="D78" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F78" s="2">
         <v>116</v>
@@ -4009,19 +4009,19 @@
     </row>
     <row r="79" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D79" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F79" s="2">
         <v>23</v>
@@ -4035,19 +4035,19 @@
     </row>
     <row r="80" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="D80" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F80" s="2">
         <v>61</v>
@@ -4061,19 +4061,19 @@
     </row>
     <row r="81" spans="1:8" ht="13" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="D81" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F81" s="2">
         <v>23</v>
